--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY4"/>
+  <dimension ref="A1:AY23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1012,6 +1012,2167 @@
       </c>
       <c r="AY4" t="inlineStr"/>
     </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>120340205</v>
+      </c>
+      <c r="B5" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>580359</v>
+      </c>
+      <c r="R5" t="n">
+        <v>7056121</v>
+      </c>
+      <c r="S5" t="n">
+        <v>10</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z5" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB5" t="inlineStr">
+        <is>
+          <t>14:54</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>120339265</v>
+      </c>
+      <c r="B6" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>580389</v>
+      </c>
+      <c r="R6" t="n">
+        <v>7056152</v>
+      </c>
+      <c r="S6" t="n">
+        <v>10</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z6" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB6" t="inlineStr">
+        <is>
+          <t>14:11</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX6" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY6" t="inlineStr"/>
+    </row>
+    <row r="7">
+      <c r="A7" t="n">
+        <v>120340499</v>
+      </c>
+      <c r="B7" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E7" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr"/>
+      <c r="P7" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q7" t="n">
+        <v>580356</v>
+      </c>
+      <c r="R7" t="n">
+        <v>7056158</v>
+      </c>
+      <c r="S7" t="n">
+        <v>10</v>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U7" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V7" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W7" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y7" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AA7" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB7" t="inlineStr">
+        <is>
+          <t>15:02</t>
+        </is>
+      </c>
+      <c r="AD7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG7" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT7" t="inlineStr"/>
+      <c r="AW7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX7" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY7" t="inlineStr"/>
+    </row>
+    <row r="8">
+      <c r="A8" t="n">
+        <v>120339582</v>
+      </c>
+      <c r="B8" t="n">
+        <v>90923</v>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E8" t="n">
+        <v>2062</v>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>Ulltickeporing</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>Skeletocutis brevispora</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
+      <c r="P8" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q8" t="n">
+        <v>580409</v>
+      </c>
+      <c r="R8" t="n">
+        <v>7056174</v>
+      </c>
+      <c r="S8" t="n">
+        <v>10</v>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U8" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V8" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W8" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AA8" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB8" t="inlineStr">
+        <is>
+          <t>14:33</t>
+        </is>
+      </c>
+      <c r="AD8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG8" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT8" t="inlineStr"/>
+      <c r="AW8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX8" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY8" t="inlineStr"/>
+    </row>
+    <row r="9">
+      <c r="A9" t="n">
+        <v>120339052</v>
+      </c>
+      <c r="B9" t="n">
+        <v>78542</v>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E9" t="n">
+        <v>6425</v>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>Garnlav</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>Alectoria sarmentosa</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr"/>
+      <c r="P9" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q9" t="n">
+        <v>580329</v>
+      </c>
+      <c r="R9" t="n">
+        <v>7056169</v>
+      </c>
+      <c r="S9" t="n">
+        <v>10</v>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U9" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V9" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W9" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AA9" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB9" t="inlineStr">
+        <is>
+          <t>14:02</t>
+        </is>
+      </c>
+      <c r="AD9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG9" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT9" t="inlineStr"/>
+      <c r="AW9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX9" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY9" t="inlineStr"/>
+    </row>
+    <row r="10">
+      <c r="A10" t="n">
+        <v>120339471</v>
+      </c>
+      <c r="B10" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E10" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="P10" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q10" t="n">
+        <v>580406</v>
+      </c>
+      <c r="R10" t="n">
+        <v>7056168</v>
+      </c>
+      <c r="S10" t="n">
+        <v>10</v>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U10" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V10" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W10" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y10" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z10" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AA10" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB10" t="inlineStr">
+        <is>
+          <t>14:26</t>
+        </is>
+      </c>
+      <c r="AD10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG10" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT10" t="inlineStr"/>
+      <c r="AW10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX10" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY10" t="inlineStr"/>
+    </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>120339749</v>
+      </c>
+      <c r="B11" t="n">
+        <v>95225</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>580421</v>
+      </c>
+      <c r="R11" t="n">
+        <v>7056111</v>
+      </c>
+      <c r="S11" t="n">
+        <v>10</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>14:39</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
+    <row r="12">
+      <c r="A12" t="n">
+        <v>120339872</v>
+      </c>
+      <c r="B12" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E12" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr"/>
+      <c r="P12" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q12" t="n">
+        <v>580419</v>
+      </c>
+      <c r="R12" t="n">
+        <v>7056080</v>
+      </c>
+      <c r="S12" t="n">
+        <v>10</v>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U12" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V12" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W12" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y12" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AA12" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB12" t="inlineStr">
+        <is>
+          <t>14:43</t>
+        </is>
+      </c>
+      <c r="AD12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG12" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT12" t="inlineStr"/>
+      <c r="AW12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX12" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY12" t="inlineStr"/>
+    </row>
+    <row r="13">
+      <c r="A13" t="n">
+        <v>120339550</v>
+      </c>
+      <c r="B13" t="n">
+        <v>90580</v>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E13" t="n">
+        <v>1202</v>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>Ullticka</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>Phellinidium ferrugineofuscum</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr"/>
+      <c r="P13" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q13" t="n">
+        <v>580411</v>
+      </c>
+      <c r="R13" t="n">
+        <v>7056175</v>
+      </c>
+      <c r="S13" t="n">
+        <v>10</v>
+      </c>
+      <c r="T13" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U13" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V13" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W13" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y13" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA13" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB13" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG13" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT13" t="inlineStr"/>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX13" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY13" t="inlineStr"/>
+    </row>
+    <row r="14">
+      <c r="A14" t="n">
+        <v>120339934</v>
+      </c>
+      <c r="B14" t="n">
+        <v>97930</v>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>VU</t>
+        </is>
+      </c>
+      <c r="E14" t="n">
+        <v>220787</v>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>Knärot</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>Goodyera repens</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>Sollefteå, Sollefteå, Ång</t>
+        </is>
+      </c>
+      <c r="Q14" t="n">
+        <v>580411</v>
+      </c>
+      <c r="R14" t="n">
+        <v>7056094</v>
+      </c>
+      <c r="S14" t="n">
+        <v>10</v>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>14:46</t>
+        </is>
+      </c>
+      <c r="AD14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG14" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT14" t="inlineStr"/>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX14" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY14" t="inlineStr"/>
+    </row>
+    <row r="15">
+      <c r="A15" t="n">
+        <v>120339080</v>
+      </c>
+      <c r="B15" t="n">
+        <v>95225</v>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E15" t="n">
+        <v>2869</v>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>Bollvitmossa</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>Sphagnum wulfianum</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr"/>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q15" t="n">
+        <v>580337</v>
+      </c>
+      <c r="R15" t="n">
+        <v>7056214</v>
+      </c>
+      <c r="S15" t="n">
+        <v>10</v>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>13:53</t>
+        </is>
+      </c>
+      <c r="AD15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG15" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT15" t="inlineStr"/>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX15" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY15" t="inlineStr"/>
+    </row>
+    <row r="16">
+      <c r="A16" t="n">
+        <v>120339150</v>
+      </c>
+      <c r="B16" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E16" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q16" t="n">
+        <v>580343</v>
+      </c>
+      <c r="R16" t="n">
+        <v>7056242</v>
+      </c>
+      <c r="S16" t="n">
+        <v>10</v>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>13:58</t>
+        </is>
+      </c>
+      <c r="AD16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG16" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT16" t="inlineStr"/>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX16" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY16" t="inlineStr"/>
+    </row>
+    <row r="17">
+      <c r="A17" t="n">
+        <v>120339911</v>
+      </c>
+      <c r="B17" t="n">
+        <v>57336</v>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E17" t="n">
+        <v>100049</v>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>Spillkråka</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>Dryocopus martius</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q17" t="n">
+        <v>580413</v>
+      </c>
+      <c r="R17" t="n">
+        <v>7056089</v>
+      </c>
+      <c r="S17" t="n">
+        <v>10</v>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>14:35</t>
+        </is>
+      </c>
+      <c r="AD17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG17" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT17" t="inlineStr"/>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX17" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY17" t="inlineStr"/>
+    </row>
+    <row r="18">
+      <c r="A18" t="n">
+        <v>120339169</v>
+      </c>
+      <c r="B18" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E18" t="n">
+        <v>658</v>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q18" t="n">
+        <v>580344</v>
+      </c>
+      <c r="R18" t="n">
+        <v>7056234</v>
+      </c>
+      <c r="S18" t="n">
+        <v>10</v>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>13:59</t>
+        </is>
+      </c>
+      <c r="AD18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG18" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT18" t="inlineStr"/>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX18" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY18" t="inlineStr"/>
+    </row>
+    <row r="19">
+      <c r="A19" t="n">
+        <v>120339013</v>
+      </c>
+      <c r="B19" t="n">
+        <v>57473</v>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E19" t="n">
+        <v>103021</v>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>Talltita</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>Poecile montanus</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q19" t="n">
+        <v>580332</v>
+      </c>
+      <c r="R19" t="n">
+        <v>7056217</v>
+      </c>
+      <c r="S19" t="n">
+        <v>25</v>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>13:50</t>
+        </is>
+      </c>
+      <c r="AD19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG19" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT19" t="inlineStr"/>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX19" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY19" t="inlineStr"/>
+    </row>
+    <row r="20">
+      <c r="A20" t="n">
+        <v>120339771</v>
+      </c>
+      <c r="B20" t="n">
+        <v>79623</v>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E20" t="n">
+        <v>6458</v>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>Lunglav</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>Lobaria pulmonaria</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+        </is>
+      </c>
+      <c r="Q20" t="n">
+        <v>580423</v>
+      </c>
+      <c r="R20" t="n">
+        <v>7056076</v>
+      </c>
+      <c r="S20" t="n">
+        <v>10</v>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>14:31</t>
+        </is>
+      </c>
+      <c r="AD20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG20" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT20" t="inlineStr"/>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX20" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY20" t="inlineStr"/>
+    </row>
+    <row r="21">
+      <c r="A21" t="n">
+        <v>120340534</v>
+      </c>
+      <c r="B21" t="n">
+        <v>57320</v>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E21" t="n">
+        <v>100109</v>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>Tretåig hackspett</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>Picoides tridactylus</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr"/>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q21" t="n">
+        <v>580366</v>
+      </c>
+      <c r="R21" t="n">
+        <v>7056169</v>
+      </c>
+      <c r="S21" t="n">
+        <v>10</v>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>15:06</t>
+        </is>
+      </c>
+      <c r="AD21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG21" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT21" t="inlineStr"/>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX21" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY21" t="inlineStr"/>
+    </row>
+    <row r="22">
+      <c r="A22" t="n">
+        <v>120339495</v>
+      </c>
+      <c r="B22" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E22" t="n">
+        <v>658</v>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr"/>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q22" t="n">
+        <v>580409</v>
+      </c>
+      <c r="R22" t="n">
+        <v>7056155</v>
+      </c>
+      <c r="S22" t="n">
+        <v>10</v>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>14:28</t>
+        </is>
+      </c>
+      <c r="AD22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG22" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT22" t="inlineStr"/>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr"/>
+    </row>
+    <row r="23">
+      <c r="A23" t="n">
+        <v>120340284</v>
+      </c>
+      <c r="B23" t="n">
+        <v>90864</v>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E23" t="n">
+        <v>658</v>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>Rosenticka</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>Rhodofomes roseus</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr"/>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>Okänd, Okänd, Ång</t>
+        </is>
+      </c>
+      <c r="Q23" t="n">
+        <v>580362</v>
+      </c>
+      <c r="R23" t="n">
+        <v>7056116</v>
+      </c>
+      <c r="S23" t="n">
+        <v>10</v>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>14:58</t>
+        </is>
+      </c>
+      <c r="AD23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG23" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT23" t="inlineStr"/>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AX23" t="inlineStr">
+        <is>
+          <t>Kim Hultgren</t>
+        </is>
+      </c>
+      <c r="AY23" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120340205</v>
+        <v>120339749</v>
       </c>
       <c r="B5" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,38 +1026,38 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580359</v>
+        <v>580421</v>
       </c>
       <c r="R5" t="n">
-        <v>7056121</v>
+        <v>7056111</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120339265</v>
+        <v>120339771</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580389</v>
+        <v>580423</v>
       </c>
       <c r="R6" t="n">
-        <v>7056152</v>
+        <v>7056076</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1226,22 +1226,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120340499</v>
+        <v>120339872</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,34 +1254,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580356</v>
+        <v>580419</v>
       </c>
       <c r="R7" t="n">
-        <v>7056158</v>
+        <v>7056080</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1313,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1323,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1350,10 +1350,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339582</v>
+        <v>120339080</v>
       </c>
       <c r="B8" t="n">
-        <v>90923</v>
+        <v>95225</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,38 +1362,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580409</v>
+        <v>580337</v>
       </c>
       <c r="R8" t="n">
-        <v>7056174</v>
+        <v>7056214</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1425,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1435,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,22 +1450,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339052</v>
+        <v>120339265</v>
       </c>
       <c r="B9" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,21 +1478,21 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
@@ -1502,10 +1502,10 @@
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580329</v>
+        <v>580389</v>
       </c>
       <c r="R9" t="n">
-        <v>7056169</v>
+        <v>7056152</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1537,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1547,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1574,10 +1574,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339471</v>
+        <v>120339911</v>
       </c>
       <c r="B10" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,34 +1590,39 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580406</v>
+        <v>580413</v>
       </c>
       <c r="R10" t="n">
-        <v>7056168</v>
+        <v>7056089</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1649,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1659,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1674,22 +1679,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339749</v>
+        <v>120339582</v>
       </c>
       <c r="B11" t="n">
-        <v>95225</v>
+        <v>90923</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1698,25 +1703,25 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
@@ -1726,10 +1731,10 @@
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580421</v>
+        <v>580409</v>
       </c>
       <c r="R11" t="n">
-        <v>7056111</v>
+        <v>7056174</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1761,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1771,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1798,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339872</v>
+        <v>120339150</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1814,34 +1819,39 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
+      <c r="M12" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580419</v>
+        <v>580343</v>
       </c>
       <c r="R12" t="n">
-        <v>7056080</v>
+        <v>7056242</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1873,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1883,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1898,19 +1908,19 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120339550</v>
+        <v>120340205</v>
       </c>
       <c r="B13" t="n">
         <v>90580</v>
@@ -1946,14 +1956,14 @@
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580411</v>
+        <v>580359</v>
       </c>
       <c r="R13" t="n">
-        <v>7056175</v>
+        <v>7056121</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1985,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -1995,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2138,10 +2148,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120339080</v>
+        <v>120340284</v>
       </c>
       <c r="B15" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2150,38 +2160,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580337</v>
+        <v>580362</v>
       </c>
       <c r="R15" t="n">
-        <v>7056214</v>
+        <v>7056116</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2213,7 +2223,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2223,7 +2233,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2238,22 +2248,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120339150</v>
+        <v>120339052</v>
       </c>
       <c r="B16" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2266,39 +2276,34 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I16" t="inlineStr"/>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580343</v>
+        <v>580329</v>
       </c>
       <c r="R16" t="n">
-        <v>7056242</v>
+        <v>7056169</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2330,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2340,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2355,22 +2360,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339911</v>
+        <v>120339169</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2383,39 +2388,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580413</v>
+        <v>580344</v>
       </c>
       <c r="R17" t="n">
-        <v>7056089</v>
+        <v>7056234</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2447,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2457,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2484,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339169</v>
+        <v>120339550</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,34 +2500,34 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580344</v>
+        <v>580411</v>
       </c>
       <c r="R18" t="n">
-        <v>7056234</v>
+        <v>7056175</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2559,7 +2559,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2569,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,22 +2584,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120339013</v>
+        <v>120340499</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>78542</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2612,51 +2612,37 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>6425</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580332</v>
+        <v>580356</v>
       </c>
       <c r="R19" t="n">
-        <v>7056217</v>
+        <v>7056158</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2671,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2681,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2696,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339771</v>
+        <v>120339013</v>
       </c>
       <c r="B20" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,37 +2724,51 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580423</v>
+        <v>580332</v>
       </c>
       <c r="R20" t="n">
-        <v>7056076</v>
+        <v>7056217</v>
       </c>
       <c r="S20" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120340284</v>
+        <v>120339471</v>
       </c>
       <c r="B23" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,34 +3079,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580362</v>
+        <v>580406</v>
       </c>
       <c r="R23" t="n">
-        <v>7056116</v>
+        <v>7056168</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339749</v>
+        <v>120339080</v>
       </c>
       <c r="B5" t="n">
         <v>95225</v>
@@ -1050,14 +1050,14 @@
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580421</v>
+        <v>580337</v>
       </c>
       <c r="R5" t="n">
-        <v>7056111</v>
+        <v>7056214</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1114,22 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120339771</v>
+        <v>120339169</v>
       </c>
       <c r="B6" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,34 +1142,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580423</v>
+        <v>580344</v>
       </c>
       <c r="R6" t="n">
-        <v>7056076</v>
+        <v>7056234</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120339872</v>
+        <v>120339911</v>
       </c>
       <c r="B7" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,34 +1254,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580419</v>
+        <v>580413</v>
       </c>
       <c r="R7" t="n">
-        <v>7056080</v>
+        <v>7056089</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1313,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1323,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1338,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339080</v>
+        <v>120340284</v>
       </c>
       <c r="B8" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1362,38 +1367,38 @@
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E8" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580337</v>
+        <v>580362</v>
       </c>
       <c r="R8" t="n">
-        <v>7056214</v>
+        <v>7056116</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1425,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1435,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1450,22 +1455,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339265</v>
+        <v>120339771</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1478,34 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580389</v>
+        <v>580423</v>
       </c>
       <c r="R9" t="n">
-        <v>7056152</v>
+        <v>7056076</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1537,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1547,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1562,22 +1567,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339911</v>
+        <v>120339052</v>
       </c>
       <c r="B10" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1590,39 +1595,34 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580413</v>
+        <v>580329</v>
       </c>
       <c r="R10" t="n">
-        <v>7056089</v>
+        <v>7056169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,22 +1679,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339582</v>
+        <v>120339265</v>
       </c>
       <c r="B11" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1703,38 +1703,38 @@
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E11" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580409</v>
+        <v>580389</v>
       </c>
       <c r="R11" t="n">
-        <v>7056174</v>
+        <v>7056152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1803,10 +1803,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339150</v>
+        <v>120339872</v>
       </c>
       <c r="B12" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1819,39 +1819,34 @@
         </is>
       </c>
       <c r="E12" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
-      <c r="M12" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580343</v>
+        <v>580419</v>
       </c>
       <c r="R12" t="n">
-        <v>7056242</v>
+        <v>7056080</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1878,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1888,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,22 +1903,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120340205</v>
+        <v>120340534</v>
       </c>
       <c r="B13" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1936,34 +1931,39 @@
         </is>
       </c>
       <c r="E13" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
+      <c r="M13" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P13" t="inlineStr">
         <is>
           <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580359</v>
+        <v>580366</v>
       </c>
       <c r="R13" t="n">
-        <v>7056121</v>
+        <v>7056169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339934</v>
+        <v>120339582</v>
       </c>
       <c r="B14" t="n">
-        <v>97930</v>
+        <v>90923</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2048,38 +2048,34 @@
         </is>
       </c>
       <c r="E14" t="n">
-        <v>220787</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Niemelä</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580411</v>
+        <v>580409</v>
       </c>
       <c r="R14" t="n">
-        <v>7056094</v>
+        <v>7056174</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2111,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2121,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2148,7 +2144,7 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120340284</v>
+        <v>120339495</v>
       </c>
       <c r="B15" t="n">
         <v>90864</v>
@@ -2188,10 +2184,10 @@
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580362</v>
+        <v>580409</v>
       </c>
       <c r="R15" t="n">
-        <v>7056116</v>
+        <v>7056155</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2223,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2233,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2260,7 +2256,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120339052</v>
+        <v>120340499</v>
       </c>
       <c r="B16" t="n">
         <v>78542</v>
@@ -2296,14 +2292,14 @@
       <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580329</v>
+        <v>580356</v>
       </c>
       <c r="R16" t="n">
-        <v>7056169</v>
+        <v>7056158</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2331,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2341,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2368,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339169</v>
+        <v>120339150</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,34 +2384,39 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580344</v>
+        <v>580343</v>
       </c>
       <c r="R17" t="n">
-        <v>7056234</v>
+        <v>7056242</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2447,7 +2448,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2457,7 +2458,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2484,10 +2485,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339550</v>
+        <v>120339013</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2500,37 +2501,51 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580411</v>
+        <v>580332</v>
       </c>
       <c r="R18" t="n">
-        <v>7056175</v>
+        <v>7056217</v>
       </c>
       <c r="S18" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2559,7 +2574,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2569,7 +2584,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2584,22 +2599,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120340499</v>
+        <v>120339934</v>
       </c>
       <c r="B19" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2608,38 +2623,42 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580356</v>
+        <v>580411</v>
       </c>
       <c r="R19" t="n">
-        <v>7056158</v>
+        <v>7056094</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2671,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2681,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2708,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339013</v>
+        <v>120340205</v>
       </c>
       <c r="B20" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2724,51 +2743,37 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580332</v>
+        <v>580359</v>
       </c>
       <c r="R20" t="n">
-        <v>7056217</v>
+        <v>7056121</v>
       </c>
       <c r="S20" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T20" t="inlineStr">
         <is>
@@ -2797,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,22 +2827,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120340534</v>
+        <v>120339550</v>
       </c>
       <c r="B21" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2850,39 +2855,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580366</v>
+        <v>580411</v>
       </c>
       <c r="R21" t="n">
-        <v>7056169</v>
+        <v>7056175</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339495</v>
+        <v>120339471</v>
       </c>
       <c r="B22" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,34 +2967,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580409</v>
+        <v>580406</v>
       </c>
       <c r="R22" t="n">
-        <v>7056155</v>
+        <v>7056168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120339471</v>
+        <v>120339749</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,25 +3075,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580406</v>
+        <v>580421</v>
       </c>
       <c r="R23" t="n">
-        <v>7056168</v>
+        <v>7056111</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339080</v>
+        <v>120339169</v>
       </c>
       <c r="B5" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1026,25 +1026,25 @@
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580337</v>
+        <v>580344</v>
       </c>
       <c r="R5" t="n">
-        <v>7056214</v>
+        <v>7056234</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120339169</v>
+        <v>120339911</v>
       </c>
       <c r="B6" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,34 +1142,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580344</v>
+        <v>580413</v>
       </c>
       <c r="R6" t="n">
-        <v>7056234</v>
+        <v>7056089</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120339911</v>
+        <v>120339080</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>95225</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1250,43 +1255,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580413</v>
+        <v>580337</v>
       </c>
       <c r="R7" t="n">
-        <v>7056089</v>
+        <v>7056214</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD7" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY23"/>
+  <dimension ref="A1:AY24"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339169</v>
+        <v>120339150</v>
       </c>
       <c r="B5" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,34 +1030,39 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
+      <c r="M5" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P5" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580344</v>
+        <v>580343</v>
       </c>
       <c r="R5" t="n">
-        <v>7056234</v>
+        <v>7056242</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1131,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120339911</v>
+        <v>120339052</v>
       </c>
       <c r="B6" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,39 +1147,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580413</v>
+        <v>580329</v>
       </c>
       <c r="R6" t="n">
-        <v>7056089</v>
+        <v>7056169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1231,22 +1231,22 @@
       <c r="AT6" t="inlineStr"/>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120339080</v>
+        <v>120340499</v>
       </c>
       <c r="B7" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1255,38 +1255,38 @@
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E7" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580337</v>
+        <v>580356</v>
       </c>
       <c r="R7" t="n">
-        <v>7056214</v>
+        <v>7056158</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,19 +1343,19 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120340284</v>
+        <v>120339495</v>
       </c>
       <c r="B8" t="n">
         <v>90864</v>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580362</v>
+        <v>580409</v>
       </c>
       <c r="R8" t="n">
-        <v>7056116</v>
+        <v>7056155</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339771</v>
+        <v>120339169</v>
       </c>
       <c r="B9" t="n">
-        <v>79623</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,34 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>6458</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580423</v>
+        <v>580344</v>
       </c>
       <c r="R9" t="n">
-        <v>7056076</v>
+        <v>7056234</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339052</v>
+        <v>120339080</v>
       </c>
       <c r="B10" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,38 +1591,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580329</v>
+        <v>580337</v>
       </c>
       <c r="R10" t="n">
-        <v>7056169</v>
+        <v>7056214</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1654,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1664,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,22 +1679,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339265</v>
+        <v>120339771</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,34 +1707,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580389</v>
+        <v>580423</v>
       </c>
       <c r="R11" t="n">
-        <v>7056152</v>
+        <v>7056076</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1766,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1776,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,12 +1791,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120340534</v>
+        <v>120339582</v>
       </c>
       <c r="B13" t="n">
-        <v>57320</v>
+        <v>90923</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,43 +1927,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>100109</v>
+        <v>2062</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
-      <c r="M13" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580366</v>
+        <v>580409</v>
       </c>
       <c r="R13" t="n">
-        <v>7056169</v>
+        <v>7056174</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1995,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2005,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2032,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339582</v>
+        <v>120339749</v>
       </c>
       <c r="B14" t="n">
-        <v>90923</v>
+        <v>95225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2044,25 +2039,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2072,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580409</v>
+        <v>580421</v>
       </c>
       <c r="R14" t="n">
-        <v>7056174</v>
+        <v>7056111</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2107,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2117,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2144,10 +2139,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120339495</v>
+        <v>120340534</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>57320</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2160,34 +2155,39 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>100109</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P15" t="inlineStr">
         <is>
           <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580409</v>
+        <v>580366</v>
       </c>
       <c r="R15" t="n">
-        <v>7056155</v>
+        <v>7056169</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2256,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120340499</v>
+        <v>120339013</v>
       </c>
       <c r="B16" t="n">
-        <v>78542</v>
+        <v>57473</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,37 +2272,51 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>6425</v>
+        <v>103021</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580356</v>
+        <v>580332</v>
       </c>
       <c r="R16" t="n">
-        <v>7056158</v>
+        <v>7056217</v>
       </c>
       <c r="S16" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2331,7 +2345,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2341,7 +2355,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2356,22 +2370,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339150</v>
+        <v>120340284</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>90864</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2384,39 +2398,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>658</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580343</v>
+        <v>580362</v>
       </c>
       <c r="R17" t="n">
-        <v>7056242</v>
+        <v>7056116</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2448,7 +2457,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2458,7 +2467,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2473,22 +2482,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339013</v>
+        <v>120339265</v>
       </c>
       <c r="B18" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,51 +2510,37 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580332</v>
+        <v>580389</v>
       </c>
       <c r="R18" t="n">
-        <v>7056217</v>
+        <v>7056152</v>
       </c>
       <c r="S18" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T18" t="inlineStr">
         <is>
@@ -2574,7 +2569,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2584,7 +2579,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2599,12 +2594,12 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
@@ -2839,7 +2834,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120339550</v>
+        <v>120339471</v>
       </c>
       <c r="B21" t="n">
         <v>90580</v>
@@ -2879,10 +2874,10 @@
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580411</v>
+        <v>580406</v>
       </c>
       <c r="R21" t="n">
-        <v>7056175</v>
+        <v>7056168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2909,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2919,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,10 +2946,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339471</v>
+        <v>120339911</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2967,34 +2962,39 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580406</v>
+        <v>580413</v>
       </c>
       <c r="R22" t="n">
-        <v>7056168</v>
+        <v>7056089</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,22 +3051,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120339749</v>
+        <v>120339550</v>
       </c>
       <c r="B23" t="n">
-        <v>95225</v>
+        <v>90580</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,25 +3075,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580421</v>
+        <v>580411</v>
       </c>
       <c r="R23" t="n">
-        <v>7056111</v>
+        <v>7056175</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3172,6 +3172,117 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+    </row>
+    <row r="24">
+      <c r="A24" t="n">
+        <v>120339349</v>
+      </c>
+      <c r="B24" t="n">
+        <v>90972</v>
+      </c>
+      <c r="C24" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E24" t="n">
+        <v>6040186</v>
+      </c>
+      <c r="G24" t="inlineStr">
+        <is>
+          <t>Leptoporus mollis</t>
+        </is>
+      </c>
+      <c r="H24" t="inlineStr">
+        <is>
+          <t>(Pers.:Fr.) Quél.</t>
+        </is>
+      </c>
+      <c r="I24" t="inlineStr"/>
+      <c r="J24" t="inlineStr"/>
+      <c r="K24" t="inlineStr"/>
+      <c r="N24" t="inlineStr"/>
+      <c r="P24" t="inlineStr">
+        <is>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+        </is>
+      </c>
+      <c r="Q24" t="n">
+        <v>580384</v>
+      </c>
+      <c r="R24" t="n">
+        <v>7056204</v>
+      </c>
+      <c r="S24" t="n">
+        <v>10</v>
+      </c>
+      <c r="T24" t="inlineStr">
+        <is>
+          <t>Västernorrland</t>
+        </is>
+      </c>
+      <c r="U24" t="inlineStr">
+        <is>
+          <t>Sollefteå</t>
+        </is>
+      </c>
+      <c r="V24" t="inlineStr">
+        <is>
+          <t>Ångermanland</t>
+        </is>
+      </c>
+      <c r="W24" t="inlineStr">
+        <is>
+          <t>Ramsele</t>
+        </is>
+      </c>
+      <c r="Y24" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="Z24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AA24" t="inlineStr">
+        <is>
+          <t>2024-10-11</t>
+        </is>
+      </c>
+      <c r="AB24" t="inlineStr">
+        <is>
+          <t>14:07</t>
+        </is>
+      </c>
+      <c r="AD24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF24" t="inlineStr"/>
+      <c r="AG24" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT24" t="inlineStr"/>
+      <c r="AW24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AX24" t="inlineStr">
+        <is>
+          <t>Kamilla Andersson</t>
+        </is>
+      </c>
+      <c r="AY24" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1915,10 +1915,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120339582</v>
+        <v>120339749</v>
       </c>
       <c r="B13" t="n">
-        <v>90923</v>
+        <v>95225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1927,25 +1927,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2062</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1955,10 +1955,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580409</v>
+        <v>580421</v>
       </c>
       <c r="R13" t="n">
-        <v>7056174</v>
+        <v>7056111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -1990,7 +1990,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2000,7 +2000,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2027,10 +2027,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339749</v>
+        <v>120339582</v>
       </c>
       <c r="B14" t="n">
-        <v>95225</v>
+        <v>90923</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,25 +2039,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>2062</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2067,10 +2067,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580421</v>
+        <v>580409</v>
       </c>
       <c r="R14" t="n">
-        <v>7056111</v>
+        <v>7056174</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2102,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2112,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2722,10 +2722,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120340205</v>
+        <v>120339911</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2738,34 +2738,39 @@
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580359</v>
+        <v>580413</v>
       </c>
       <c r="R20" t="n">
-        <v>7056121</v>
+        <v>7056089</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2822,19 +2827,19 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120339471</v>
+        <v>120340205</v>
       </c>
       <c r="B21" t="n">
         <v>90580</v>
@@ -2870,14 +2875,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580406</v>
+        <v>580359</v>
       </c>
       <c r="R21" t="n">
-        <v>7056168</v>
+        <v>7056121</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2946,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339911</v>
+        <v>120339471</v>
       </c>
       <c r="B22" t="n">
-        <v>57336</v>
+        <v>90580</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,39 +2967,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>100049</v>
+        <v>1202</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580413</v>
+        <v>580406</v>
       </c>
       <c r="R22" t="n">
-        <v>7056089</v>
+        <v>7056168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3051,12 +3051,12 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339150</v>
+        <v>120339911</v>
       </c>
       <c r="B5" t="n">
         <v>57336</v>
@@ -1059,10 +1059,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580343</v>
+        <v>580413</v>
       </c>
       <c r="R5" t="n">
-        <v>7056242</v>
+        <v>7056089</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1094,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1104,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1131,7 +1131,7 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120339052</v>
+        <v>120340499</v>
       </c>
       <c r="B6" t="n">
         <v>78542</v>
@@ -1167,14 +1167,14 @@
       <c r="I6" t="inlineStr"/>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580329</v>
+        <v>580356</v>
       </c>
       <c r="R6" t="n">
-        <v>7056169</v>
+        <v>7056158</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,7 +1243,7 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120340499</v>
+        <v>120339052</v>
       </c>
       <c r="B7" t="n">
         <v>78542</v>
@@ -1279,14 +1279,14 @@
       <c r="I7" t="inlineStr"/>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580356</v>
+        <v>580329</v>
       </c>
       <c r="R7" t="n">
-        <v>7056158</v>
+        <v>7056169</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339495</v>
+        <v>120339013</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,37 +1371,51 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M8" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580409</v>
+        <v>580332</v>
       </c>
       <c r="R8" t="n">
-        <v>7056155</v>
+        <v>7056217</v>
       </c>
       <c r="S8" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1430,7 +1444,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1454,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1455,22 +1469,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339169</v>
+        <v>120339582</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>90923</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1479,38 +1493,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>2062</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580344</v>
+        <v>580409</v>
       </c>
       <c r="R9" t="n">
-        <v>7056234</v>
+        <v>7056174</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339080</v>
+        <v>120340284</v>
       </c>
       <c r="B10" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,38 +1605,38 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580337</v>
+        <v>580362</v>
       </c>
       <c r="R10" t="n">
-        <v>7056214</v>
+        <v>7056116</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1654,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1664,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1679,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339771</v>
+        <v>120339265</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>90580</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1707,34 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>1202</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580423</v>
+        <v>580389</v>
       </c>
       <c r="R11" t="n">
-        <v>7056076</v>
+        <v>7056152</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1766,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1776,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1791,12 +1805,12 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
@@ -2027,10 +2041,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339582</v>
+        <v>120339495</v>
       </c>
       <c r="B14" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2039,38 +2053,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
         <v>580409</v>
       </c>
       <c r="R14" t="n">
-        <v>7056174</v>
+        <v>7056155</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2102,7 +2116,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2112,7 +2126,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2139,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120340534</v>
+        <v>120339169</v>
       </c>
       <c r="B15" t="n">
-        <v>57320</v>
+        <v>90864</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2155,39 +2169,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>100109</v>
+        <v>658</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580366</v>
+        <v>580344</v>
       </c>
       <c r="R15" t="n">
-        <v>7056169</v>
+        <v>7056234</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2244,22 +2253,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120339013</v>
+        <v>120340205</v>
       </c>
       <c r="B16" t="n">
-        <v>57473</v>
+        <v>90580</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2272,51 +2281,37 @@
         </is>
       </c>
       <c r="E16" t="n">
-        <v>103021</v>
+        <v>1202</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580332</v>
+        <v>580359</v>
       </c>
       <c r="R16" t="n">
-        <v>7056217</v>
+        <v>7056121</v>
       </c>
       <c r="S16" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T16" t="inlineStr">
         <is>
@@ -2345,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2355,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2370,22 +2365,22 @@
       <c r="AT16" t="inlineStr"/>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120340284</v>
+        <v>120339934</v>
       </c>
       <c r="B17" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2394,38 +2389,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580362</v>
+        <v>580411</v>
       </c>
       <c r="R17" t="n">
-        <v>7056116</v>
+        <v>7056094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2457,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2467,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2494,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339265</v>
+        <v>120339150</v>
       </c>
       <c r="B18" t="n">
-        <v>90580</v>
+        <v>57336</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,34 +2509,39 @@
         </is>
       </c>
       <c r="E18" t="n">
-        <v>1202</v>
+        <v>100049</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580389</v>
+        <v>580343</v>
       </c>
       <c r="R18" t="n">
-        <v>7056152</v>
+        <v>7056242</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2569,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2579,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2594,22 +2598,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120339934</v>
+        <v>120340534</v>
       </c>
       <c r="B19" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2618,42 +2622,43 @@
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E19" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580411</v>
+        <v>580366</v>
       </c>
       <c r="R19" t="n">
-        <v>7056094</v>
+        <v>7056169</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2722,10 +2727,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339911</v>
+        <v>120339080</v>
       </c>
       <c r="B20" t="n">
-        <v>57336</v>
+        <v>95225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,43 +2739,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>100049</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P20" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580413</v>
+        <v>580337</v>
       </c>
       <c r="R20" t="n">
-        <v>7056089</v>
+        <v>7056214</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2839,7 +2839,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120340205</v>
+        <v>120339471</v>
       </c>
       <c r="B21" t="n">
         <v>90580</v>
@@ -2875,14 +2875,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580359</v>
+        <v>580406</v>
       </c>
       <c r="R21" t="n">
-        <v>7056121</v>
+        <v>7056168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,7 +2951,7 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339471</v>
+        <v>120339550</v>
       </c>
       <c r="B22" t="n">
         <v>90580</v>
@@ -2991,10 +2991,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580406</v>
+        <v>580411</v>
       </c>
       <c r="R22" t="n">
-        <v>7056168</v>
+        <v>7056175</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120339550</v>
+        <v>120339771</v>
       </c>
       <c r="B23" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,34 +3079,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580411</v>
+        <v>580423</v>
       </c>
       <c r="R23" t="n">
-        <v>7056175</v>
+        <v>7056076</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3163,12 +3163,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339911</v>
+        <v>120340499</v>
       </c>
       <c r="B5" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,39 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580413</v>
+        <v>580356</v>
       </c>
       <c r="R5" t="n">
-        <v>7056089</v>
+        <v>7056158</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1094,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1104,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1119,22 +1114,22 @@
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120340499</v>
+        <v>120340534</v>
       </c>
       <c r="B6" t="n">
-        <v>78542</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1147,34 +1142,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>6425</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580356</v>
+        <v>580366</v>
       </c>
       <c r="R6" t="n">
-        <v>7056158</v>
+        <v>7056169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120339052</v>
+        <v>120340284</v>
       </c>
       <c r="B7" t="n">
-        <v>78542</v>
+        <v>90864</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,21 +1259,21 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
@@ -1283,10 +1283,10 @@
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580329</v>
+        <v>580362</v>
       </c>
       <c r="R7" t="n">
-        <v>7056169</v>
+        <v>7056116</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339013</v>
+        <v>120339495</v>
       </c>
       <c r="B8" t="n">
-        <v>57473</v>
+        <v>90864</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,51 +1371,37 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M8" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr"/>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580332</v>
+        <v>580409</v>
       </c>
       <c r="R8" t="n">
-        <v>7056217</v>
+        <v>7056155</v>
       </c>
       <c r="S8" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T8" t="inlineStr">
         <is>
@@ -1444,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1454,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1469,22 +1455,22 @@
       <c r="AT8" t="inlineStr"/>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339582</v>
+        <v>120340205</v>
       </c>
       <c r="B9" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1493,38 +1479,38 @@
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E9" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580409</v>
+        <v>580359</v>
       </c>
       <c r="R9" t="n">
-        <v>7056174</v>
+        <v>7056121</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1556,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1566,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1593,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120340284</v>
+        <v>120339934</v>
       </c>
       <c r="B10" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1605,38 +1591,42 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580362</v>
+        <v>580411</v>
       </c>
       <c r="R10" t="n">
-        <v>7056116</v>
+        <v>7056094</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1668,7 +1658,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1668,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1705,10 +1695,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339265</v>
+        <v>120339013</v>
       </c>
       <c r="B11" t="n">
-        <v>90580</v>
+        <v>57473</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1721,37 +1711,51 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>1202</v>
+        <v>103021</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580389</v>
+        <v>580332</v>
       </c>
       <c r="R11" t="n">
-        <v>7056152</v>
+        <v>7056217</v>
       </c>
       <c r="S11" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1780,7 +1784,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1790,7 +1794,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1805,22 +1809,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339872</v>
+        <v>120339749</v>
       </c>
       <c r="B12" t="n">
-        <v>79623</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1829,38 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580419</v>
+        <v>580421</v>
       </c>
       <c r="R12" t="n">
-        <v>7056080</v>
+        <v>7056111</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1892,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1902,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1929,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120339749</v>
+        <v>120339052</v>
       </c>
       <c r="B13" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1941,38 +1945,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580421</v>
+        <v>580329</v>
       </c>
       <c r="R13" t="n">
-        <v>7056111</v>
+        <v>7056169</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2004,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2014,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2041,10 +2045,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339495</v>
+        <v>120339080</v>
       </c>
       <c r="B14" t="n">
-        <v>90864</v>
+        <v>95225</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2053,38 +2057,38 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>658</v>
+        <v>2869</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
       <c r="P14" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580409</v>
+        <v>580337</v>
       </c>
       <c r="R14" t="n">
-        <v>7056155</v>
+        <v>7056214</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2116,7 +2120,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2126,7 +2130,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2141,22 +2145,22 @@
       <c r="AT14" t="inlineStr"/>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120339169</v>
+        <v>120339771</v>
       </c>
       <c r="B15" t="n">
-        <v>90864</v>
+        <v>79623</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,34 +2173,34 @@
         </is>
       </c>
       <c r="E15" t="n">
-        <v>658</v>
+        <v>6458</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580344</v>
+        <v>580423</v>
       </c>
       <c r="R15" t="n">
-        <v>7056234</v>
+        <v>7056076</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2228,7 +2232,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2238,7 +2242,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2265,7 +2269,7 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120340205</v>
+        <v>120339265</v>
       </c>
       <c r="B16" t="n">
         <v>90580</v>
@@ -2305,10 +2309,10 @@
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580359</v>
+        <v>580389</v>
       </c>
       <c r="R16" t="n">
-        <v>7056121</v>
+        <v>7056152</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2340,7 +2344,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2350,7 +2354,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2377,10 +2381,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339934</v>
+        <v>120339911</v>
       </c>
       <c r="B17" t="n">
-        <v>97930</v>
+        <v>57336</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,42 +2393,43 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>220787</v>
+        <v>100049</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr"/>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580411</v>
+        <v>580413</v>
       </c>
       <c r="R17" t="n">
-        <v>7056094</v>
+        <v>7056089</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2456,7 +2461,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2466,7 +2471,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2481,22 +2486,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339150</v>
+        <v>120339582</v>
       </c>
       <c r="B18" t="n">
-        <v>57336</v>
+        <v>90923</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2505,43 +2510,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>100049</v>
+        <v>2062</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580343</v>
+        <v>580409</v>
       </c>
       <c r="R18" t="n">
-        <v>7056242</v>
+        <v>7056174</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2573,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2583,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2598,22 +2598,22 @@
       <c r="AT18" t="inlineStr"/>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120340534</v>
+        <v>120339872</v>
       </c>
       <c r="B19" t="n">
-        <v>57320</v>
+        <v>79623</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,39 +2626,34 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>100109</v>
+        <v>6458</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I19" t="inlineStr"/>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P19" t="inlineStr">
         <is>
           <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580366</v>
+        <v>580419</v>
       </c>
       <c r="R19" t="n">
-        <v>7056169</v>
+        <v>7056080</v>
       </c>
       <c r="S19" t="n">
         <v>10</v>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2722,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339080</v>
+        <v>120339550</v>
       </c>
       <c r="B20" t="n">
-        <v>95225</v>
+        <v>90580</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,38 +2734,38 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580337</v>
+        <v>580411</v>
       </c>
       <c r="R20" t="n">
-        <v>7056214</v>
+        <v>7056175</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2797,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2807,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2822,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120339471</v>
+        <v>120339169</v>
       </c>
       <c r="B21" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,34 +2850,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580406</v>
+        <v>580344</v>
       </c>
       <c r="R21" t="n">
-        <v>7056168</v>
+        <v>7056234</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2909,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2919,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2939,19 +2934,19 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339550</v>
+        <v>120339471</v>
       </c>
       <c r="B22" t="n">
         <v>90580</v>
@@ -2991,10 +2986,10 @@
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580411</v>
+        <v>580406</v>
       </c>
       <c r="R22" t="n">
-        <v>7056175</v>
+        <v>7056168</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3021,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3031,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,10 +3058,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120339771</v>
+        <v>120339150</v>
       </c>
       <c r="B23" t="n">
-        <v>79623</v>
+        <v>57336</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3079,34 +3074,39 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6458</v>
+        <v>100049</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580423</v>
+        <v>580343</v>
       </c>
       <c r="R23" t="n">
-        <v>7056076</v>
+        <v>7056242</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1821,10 +1821,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339749</v>
+        <v>120339052</v>
       </c>
       <c r="B12" t="n">
-        <v>95225</v>
+        <v>78542</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1833,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>6425</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580421</v>
+        <v>580329</v>
       </c>
       <c r="R12" t="n">
-        <v>7056111</v>
+        <v>7056169</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1896,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1906,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1933,10 +1933,10 @@
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120339052</v>
+        <v>120339749</v>
       </c>
       <c r="B13" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,38 +1945,38 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
       <c r="P13" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580329</v>
+        <v>580421</v>
       </c>
       <c r="R13" t="n">
-        <v>7056169</v>
+        <v>7056111</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +2008,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2018,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD13" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,10 +1014,10 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120340499</v>
+        <v>120339265</v>
       </c>
       <c r="B5" t="n">
-        <v>78542</v>
+        <v>90580</v>
       </c>
       <c r="C5" t="inlineStr">
         <is>
@@ -1030,34 +1030,34 @@
         </is>
       </c>
       <c r="E5" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580356</v>
+        <v>580389</v>
       </c>
       <c r="R5" t="n">
-        <v>7056158</v>
+        <v>7056152</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120340534</v>
+        <v>120340205</v>
       </c>
       <c r="B6" t="n">
-        <v>57320</v>
+        <v>90580</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,39 +1142,34 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>100109</v>
+        <v>1202</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
-      <c r="M6" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580366</v>
+        <v>580359</v>
       </c>
       <c r="R6" t="n">
-        <v>7056169</v>
+        <v>7056121</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1206,7 +1201,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1216,7 +1211,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1243,10 +1238,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120340284</v>
+        <v>120339150</v>
       </c>
       <c r="B7" t="n">
-        <v>90864</v>
+        <v>57336</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1259,34 +1254,39 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>658</v>
+        <v>100049</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
+      <c r="M7" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580362</v>
+        <v>580343</v>
       </c>
       <c r="R7" t="n">
-        <v>7056116</v>
+        <v>7056242</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1343,22 +1343,22 @@
       <c r="AT7" t="inlineStr"/>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339495</v>
+        <v>120339052</v>
       </c>
       <c r="B8" t="n">
-        <v>90864</v>
+        <v>78542</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580409</v>
+        <v>580329</v>
       </c>
       <c r="R8" t="n">
-        <v>7056155</v>
+        <v>7056169</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,7 +1467,7 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120340205</v>
+        <v>120339471</v>
       </c>
       <c r="B9" t="n">
         <v>90580</v>
@@ -1503,14 +1503,14 @@
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580359</v>
+        <v>580406</v>
       </c>
       <c r="R9" t="n">
-        <v>7056121</v>
+        <v>7056168</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339934</v>
+        <v>120340534</v>
       </c>
       <c r="B10" t="n">
-        <v>97930</v>
+        <v>57320</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1591,42 +1591,43 @@
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E10" t="n">
-        <v>220787</v>
+        <v>100109</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>20</t>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
+      <c r="M10" t="inlineStr">
+        <is>
+          <t>färska spår</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580411</v>
+        <v>580366</v>
       </c>
       <c r="R10" t="n">
-        <v>7056094</v>
+        <v>7056169</v>
       </c>
       <c r="S10" t="n">
         <v>10</v>
@@ -1658,7 +1659,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1668,7 +1669,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1695,10 +1696,10 @@
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339013</v>
+        <v>120339872</v>
       </c>
       <c r="B11" t="n">
-        <v>57473</v>
+        <v>79623</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1711,51 +1712,37 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M11" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580332</v>
+        <v>580419</v>
       </c>
       <c r="R11" t="n">
-        <v>7056217</v>
+        <v>7056080</v>
       </c>
       <c r="S11" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T11" t="inlineStr">
         <is>
@@ -1784,7 +1771,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1794,7 +1781,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1809,22 +1796,22 @@
       <c r="AT11" t="inlineStr"/>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339052</v>
+        <v>120339080</v>
       </c>
       <c r="B12" t="n">
-        <v>78542</v>
+        <v>95225</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1833,38 +1820,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>6425</v>
+        <v>2869</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580329</v>
+        <v>580337</v>
       </c>
       <c r="R12" t="n">
-        <v>7056169</v>
+        <v>7056214</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1896,7 +1883,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1906,7 +1893,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1921,22 +1908,22 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="n">
-        <v>120339749</v>
+        <v>120339550</v>
       </c>
       <c r="B13" t="n">
-        <v>95225</v>
+        <v>90580</v>
       </c>
       <c r="C13" t="inlineStr">
         <is>
@@ -1945,25 +1932,25 @@
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E13" t="n">
-        <v>2869</v>
+        <v>1202</v>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I13" t="inlineStr"/>
@@ -1973,10 +1960,10 @@
         </is>
       </c>
       <c r="Q13" t="n">
-        <v>580421</v>
+        <v>580411</v>
       </c>
       <c r="R13" t="n">
-        <v>7056111</v>
+        <v>7056175</v>
       </c>
       <c r="S13" t="n">
         <v>10</v>
@@ -2008,7 +1995,7 @@
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
@@ -2018,7 +2005,7 @@
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD13" t="b">
@@ -2045,10 +2032,10 @@
     </row>
     <row r="14">
       <c r="A14" t="n">
-        <v>120339080</v>
+        <v>120339169</v>
       </c>
       <c r="B14" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C14" t="inlineStr">
         <is>
@@ -2057,25 +2044,25 @@
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E14" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I14" t="inlineStr"/>
@@ -2085,10 +2072,10 @@
         </is>
       </c>
       <c r="Q14" t="n">
-        <v>580337</v>
+        <v>580344</v>
       </c>
       <c r="R14" t="n">
-        <v>7056214</v>
+        <v>7056234</v>
       </c>
       <c r="S14" t="n">
         <v>10</v>
@@ -2120,7 +2107,7 @@
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
@@ -2130,7 +2117,7 @@
       </c>
       <c r="AB14" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>13:59</t>
         </is>
       </c>
       <c r="AD14" t="b">
@@ -2157,10 +2144,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120339771</v>
+        <v>120339582</v>
       </c>
       <c r="B15" t="n">
-        <v>79623</v>
+        <v>90923</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2169,38 +2156,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>6458</v>
+        <v>2062</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580423</v>
+        <v>580409</v>
       </c>
       <c r="R15" t="n">
-        <v>7056076</v>
+        <v>7056174</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2232,7 +2219,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2242,7 +2229,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2257,22 +2244,22 @@
       <c r="AT15" t="inlineStr"/>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120339265</v>
+        <v>120339934</v>
       </c>
       <c r="B16" t="n">
-        <v>90580</v>
+        <v>97930</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2281,38 +2268,42 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580389</v>
+        <v>580411</v>
       </c>
       <c r="R16" t="n">
-        <v>7056152</v>
+        <v>7056094</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2344,7 +2335,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2354,7 +2345,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2498,10 +2489,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339582</v>
+        <v>120339495</v>
       </c>
       <c r="B18" t="n">
-        <v>90923</v>
+        <v>90864</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2510,38 +2501,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>2062</v>
+        <v>658</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
         <v>580409</v>
       </c>
       <c r="R18" t="n">
-        <v>7056174</v>
+        <v>7056155</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2573,7 +2564,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2583,7 +2574,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2610,10 +2601,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120339872</v>
+        <v>120339013</v>
       </c>
       <c r="B19" t="n">
-        <v>79623</v>
+        <v>57473</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2626,37 +2617,51 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>6458</v>
+        <v>103021</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P19" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580419</v>
+        <v>580332</v>
       </c>
       <c r="R19" t="n">
-        <v>7056080</v>
+        <v>7056217</v>
       </c>
       <c r="S19" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2685,7 +2690,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2695,7 +2700,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2710,22 +2715,22 @@
       <c r="AT19" t="inlineStr"/>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339550</v>
+        <v>120339749</v>
       </c>
       <c r="B20" t="n">
-        <v>90580</v>
+        <v>95225</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2734,25 +2739,25 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>1202</v>
+        <v>2869</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
@@ -2762,10 +2767,10 @@
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580411</v>
+        <v>580421</v>
       </c>
       <c r="R20" t="n">
-        <v>7056175</v>
+        <v>7056111</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2797,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2807,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2834,7 +2839,7 @@
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120339169</v>
+        <v>120340284</v>
       </c>
       <c r="B21" t="n">
         <v>90864</v>
@@ -2870,14 +2875,14 @@
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580344</v>
+        <v>580362</v>
       </c>
       <c r="R21" t="n">
-        <v>7056234</v>
+        <v>7056116</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2909,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2919,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>13:59</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2934,22 +2939,22 @@
       <c r="AT21" t="inlineStr"/>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339471</v>
+        <v>120339771</v>
       </c>
       <c r="B22" t="n">
-        <v>90580</v>
+        <v>79623</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2962,34 +2967,34 @@
         </is>
       </c>
       <c r="E22" t="n">
-        <v>1202</v>
+        <v>6458</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580406</v>
+        <v>580423</v>
       </c>
       <c r="R22" t="n">
-        <v>7056168</v>
+        <v>7056076</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3021,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3031,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3046,22 +3051,22 @@
       <c r="AT22" t="inlineStr"/>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120339150</v>
+        <v>120340499</v>
       </c>
       <c r="B23" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3074,39 +3079,34 @@
         </is>
       </c>
       <c r="E23" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P23" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580343</v>
+        <v>580356</v>
       </c>
       <c r="R23" t="n">
-        <v>7056242</v>
+        <v>7056158</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD23" t="b">
@@ -3163,12 +3163,12 @@
       <c r="AT23" t="inlineStr"/>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1014,7 +1014,7 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>120339265</v>
+        <v>120340205</v>
       </c>
       <c r="B5" t="n">
         <v>90580</v>
@@ -1054,10 +1054,10 @@
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>580389</v>
+        <v>580359</v>
       </c>
       <c r="R5" t="n">
-        <v>7056152</v>
+        <v>7056121</v>
       </c>
       <c r="S5" t="n">
         <v>10</v>
@@ -1089,7 +1089,7 @@
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
@@ -1099,7 +1099,7 @@
       </c>
       <c r="AB5" t="inlineStr">
         <is>
-          <t>14:11</t>
+          <t>14:54</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1126,10 +1126,10 @@
     </row>
     <row r="6">
       <c r="A6" t="n">
-        <v>120340205</v>
+        <v>120340534</v>
       </c>
       <c r="B6" t="n">
-        <v>90580</v>
+        <v>57320</v>
       </c>
       <c r="C6" t="inlineStr">
         <is>
@@ -1142,34 +1142,39 @@
         </is>
       </c>
       <c r="E6" t="n">
-        <v>1202</v>
+        <v>100109</v>
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Tretåig hackspett</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Picoides tridactylus</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I6" t="inlineStr"/>
+      <c r="M6" t="inlineStr">
+        <is>
+          <t>färska spår</t>
+        </is>
+      </c>
       <c r="P6" t="inlineStr">
         <is>
           <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q6" t="n">
-        <v>580359</v>
+        <v>580366</v>
       </c>
       <c r="R6" t="n">
-        <v>7056121</v>
+        <v>7056169</v>
       </c>
       <c r="S6" t="n">
         <v>10</v>
@@ -1201,7 +1206,7 @@
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
@@ -1211,7 +1216,7 @@
       </c>
       <c r="AB6" t="inlineStr">
         <is>
-          <t>14:54</t>
+          <t>15:06</t>
         </is>
       </c>
       <c r="AD6" t="b">
@@ -1238,10 +1243,10 @@
     </row>
     <row r="7">
       <c r="A7" t="n">
-        <v>120339150</v>
+        <v>120339771</v>
       </c>
       <c r="B7" t="n">
-        <v>57336</v>
+        <v>79623</v>
       </c>
       <c r="C7" t="inlineStr">
         <is>
@@ -1254,39 +1259,34 @@
         </is>
       </c>
       <c r="E7" t="n">
-        <v>100049</v>
+        <v>6458</v>
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I7" t="inlineStr"/>
-      <c r="M7" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
         </is>
       </c>
       <c r="Q7" t="n">
-        <v>580343</v>
+        <v>580423</v>
       </c>
       <c r="R7" t="n">
-        <v>7056242</v>
+        <v>7056076</v>
       </c>
       <c r="S7" t="n">
         <v>10</v>
@@ -1318,7 +1318,7 @@
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="AB7" t="inlineStr">
         <is>
-          <t>13:58</t>
+          <t>14:31</t>
         </is>
       </c>
       <c r="AD7" t="b">
@@ -1355,10 +1355,10 @@
     </row>
     <row r="8">
       <c r="A8" t="n">
-        <v>120339052</v>
+        <v>120339872</v>
       </c>
       <c r="B8" t="n">
-        <v>78542</v>
+        <v>79623</v>
       </c>
       <c r="C8" t="inlineStr">
         <is>
@@ -1371,21 +1371,21 @@
         </is>
       </c>
       <c r="E8" t="n">
-        <v>6425</v>
+        <v>6458</v>
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I8" t="inlineStr"/>
@@ -1395,10 +1395,10 @@
         </is>
       </c>
       <c r="Q8" t="n">
-        <v>580329</v>
+        <v>580419</v>
       </c>
       <c r="R8" t="n">
-        <v>7056169</v>
+        <v>7056080</v>
       </c>
       <c r="S8" t="n">
         <v>10</v>
@@ -1430,7 +1430,7 @@
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -1440,7 +1440,7 @@
       </c>
       <c r="AB8" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:43</t>
         </is>
       </c>
       <c r="AD8" t="b">
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339471</v>
+        <v>120339495</v>
       </c>
       <c r="B9" t="n">
-        <v>90580</v>
+        <v>90864</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,34 +1483,34 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I9" t="inlineStr"/>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580406</v>
+        <v>580409</v>
       </c>
       <c r="R9" t="n">
-        <v>7056168</v>
+        <v>7056155</v>
       </c>
       <c r="S9" t="n">
         <v>10</v>
@@ -1542,7 +1542,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1552,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:26</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1579,10 +1579,10 @@
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120340534</v>
+        <v>120339013</v>
       </c>
       <c r="B10" t="n">
-        <v>57320</v>
+        <v>57473</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,42 +1595,51 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>100109</v>
+        <v>103021</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Tretåig hackspett</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Picoides tridactylus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
       <c r="M10" t="inlineStr">
         <is>
-          <t>färska spår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580366</v>
+        <v>580332</v>
       </c>
       <c r="R10" t="n">
-        <v>7056169</v>
+        <v>7056217</v>
       </c>
       <c r="S10" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1659,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1669,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>15:06</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1684,22 +1693,22 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="n">
-        <v>120339872</v>
+        <v>120340499</v>
       </c>
       <c r="B11" t="n">
-        <v>79623</v>
+        <v>78542</v>
       </c>
       <c r="C11" t="inlineStr">
         <is>
@@ -1712,34 +1721,34 @@
         </is>
       </c>
       <c r="E11" t="n">
-        <v>6458</v>
+        <v>6425</v>
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I11" t="inlineStr"/>
       <c r="P11" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q11" t="n">
-        <v>580419</v>
+        <v>580356</v>
       </c>
       <c r="R11" t="n">
-        <v>7056080</v>
+        <v>7056158</v>
       </c>
       <c r="S11" t="n">
         <v>10</v>
@@ -1771,7 +1780,7 @@
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
@@ -1781,7 +1790,7 @@
       </c>
       <c r="AB11" t="inlineStr">
         <is>
-          <t>14:43</t>
+          <t>15:02</t>
         </is>
       </c>
       <c r="AD11" t="b">
@@ -1808,10 +1817,10 @@
     </row>
     <row r="12">
       <c r="A12" t="n">
-        <v>120339080</v>
+        <v>120340284</v>
       </c>
       <c r="B12" t="n">
-        <v>95225</v>
+        <v>90864</v>
       </c>
       <c r="C12" t="inlineStr">
         <is>
@@ -1820,38 +1829,38 @@
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E12" t="n">
-        <v>2869</v>
+        <v>658</v>
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I12" t="inlineStr"/>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q12" t="n">
-        <v>580337</v>
+        <v>580362</v>
       </c>
       <c r="R12" t="n">
-        <v>7056214</v>
+        <v>7056116</v>
       </c>
       <c r="S12" t="n">
         <v>10</v>
@@ -1883,7 +1892,7 @@
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -1893,7 +1902,7 @@
       </c>
       <c r="AB12" t="inlineStr">
         <is>
-          <t>13:53</t>
+          <t>14:58</t>
         </is>
       </c>
       <c r="AD12" t="b">
@@ -1908,12 +1917,12 @@
       <c r="AT12" t="inlineStr"/>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
@@ -2144,10 +2153,10 @@
     </row>
     <row r="15">
       <c r="A15" t="n">
-        <v>120339582</v>
+        <v>120339265</v>
       </c>
       <c r="B15" t="n">
-        <v>90923</v>
+        <v>90580</v>
       </c>
       <c r="C15" t="inlineStr">
         <is>
@@ -2156,38 +2165,38 @@
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E15" t="n">
-        <v>2062</v>
+        <v>1202</v>
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>Ulltickeporing</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
         <is>
-          <t>Skeletocutis brevispora</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>Niemelä</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I15" t="inlineStr"/>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q15" t="n">
-        <v>580409</v>
+        <v>580389</v>
       </c>
       <c r="R15" t="n">
-        <v>7056174</v>
+        <v>7056152</v>
       </c>
       <c r="S15" t="n">
         <v>10</v>
@@ -2219,7 +2228,7 @@
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
@@ -2229,7 +2238,7 @@
       </c>
       <c r="AB15" t="inlineStr">
         <is>
-          <t>14:33</t>
+          <t>14:11</t>
         </is>
       </c>
       <c r="AD15" t="b">
@@ -2256,10 +2265,10 @@
     </row>
     <row r="16">
       <c r="A16" t="n">
-        <v>120339934</v>
+        <v>120339749</v>
       </c>
       <c r="B16" t="n">
-        <v>97930</v>
+        <v>95225</v>
       </c>
       <c r="C16" t="inlineStr">
         <is>
@@ -2268,42 +2277,38 @@
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E16" t="n">
-        <v>220787</v>
+        <v>2869</v>
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>Girg.</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr"/>
       <c r="P16" t="inlineStr">
         <is>
           <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q16" t="n">
-        <v>580411</v>
+        <v>580421</v>
       </c>
       <c r="R16" t="n">
-        <v>7056094</v>
+        <v>7056111</v>
       </c>
       <c r="S16" t="n">
         <v>10</v>
@@ -2335,7 +2340,7 @@
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
@@ -2345,7 +2350,7 @@
       </c>
       <c r="AB16" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:39</t>
         </is>
       </c>
       <c r="AD16" t="b">
@@ -2372,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339911</v>
+        <v>120339052</v>
       </c>
       <c r="B17" t="n">
-        <v>57336</v>
+        <v>78542</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2388,39 +2393,34 @@
         </is>
       </c>
       <c r="E17" t="n">
-        <v>100049</v>
+        <v>6425</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I17" t="inlineStr"/>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580413</v>
+        <v>580329</v>
       </c>
       <c r="R17" t="n">
-        <v>7056089</v>
+        <v>7056169</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2452,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2462,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:35</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2477,22 +2477,22 @@
       <c r="AT17" t="inlineStr"/>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339495</v>
+        <v>120339934</v>
       </c>
       <c r="B18" t="n">
-        <v>90864</v>
+        <v>97930</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,38 +2501,42 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580409</v>
+        <v>580411</v>
       </c>
       <c r="R18" t="n">
-        <v>7056155</v>
+        <v>7056094</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2564,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2574,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD18" t="b">
@@ -2601,10 +2605,10 @@
     </row>
     <row r="19">
       <c r="A19" t="n">
-        <v>120339013</v>
+        <v>120339911</v>
       </c>
       <c r="B19" t="n">
-        <v>57473</v>
+        <v>57336</v>
       </c>
       <c r="C19" t="inlineStr">
         <is>
@@ -2617,36 +2621,27 @@
         </is>
       </c>
       <c r="E19" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr"/>
       <c r="M19" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>äldre spår</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2655,13 +2650,13 @@
         </is>
       </c>
       <c r="Q19" t="n">
-        <v>580332</v>
+        <v>580413</v>
       </c>
       <c r="R19" t="n">
-        <v>7056217</v>
+        <v>7056089</v>
       </c>
       <c r="S19" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T19" t="inlineStr">
         <is>
@@ -2690,7 +2685,7 @@
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
@@ -2700,7 +2695,7 @@
       </c>
       <c r="AB19" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:35</t>
         </is>
       </c>
       <c r="AD19" t="b">
@@ -2727,10 +2722,10 @@
     </row>
     <row r="20">
       <c r="A20" t="n">
-        <v>120339749</v>
+        <v>120339150</v>
       </c>
       <c r="B20" t="n">
-        <v>95225</v>
+        <v>57336</v>
       </c>
       <c r="C20" t="inlineStr">
         <is>
@@ -2739,38 +2734,43 @@
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E20" t="n">
-        <v>2869</v>
+        <v>100049</v>
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>Bollvitmossa</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
         <is>
-          <t>Sphagnum wulfianum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>Girg.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I20" t="inlineStr"/>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q20" t="n">
-        <v>580421</v>
+        <v>580343</v>
       </c>
       <c r="R20" t="n">
-        <v>7056111</v>
+        <v>7056242</v>
       </c>
       <c r="S20" t="n">
         <v>10</v>
@@ -2802,7 +2802,7 @@
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
@@ -2812,7 +2812,7 @@
       </c>
       <c r="AB20" t="inlineStr">
         <is>
-          <t>14:39</t>
+          <t>13:58</t>
         </is>
       </c>
       <c r="AD20" t="b">
@@ -2827,22 +2827,22 @@
       <c r="AT20" t="inlineStr"/>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" t="n">
-        <v>120340284</v>
+        <v>120339471</v>
       </c>
       <c r="B21" t="n">
-        <v>90864</v>
+        <v>90580</v>
       </c>
       <c r="C21" t="inlineStr">
         <is>
@@ -2855,34 +2855,34 @@
         </is>
       </c>
       <c r="E21" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I21" t="inlineStr"/>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q21" t="n">
-        <v>580362</v>
+        <v>580406</v>
       </c>
       <c r="R21" t="n">
-        <v>7056116</v>
+        <v>7056168</v>
       </c>
       <c r="S21" t="n">
         <v>10</v>
@@ -2914,7 +2914,7 @@
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
@@ -2924,7 +2924,7 @@
       </c>
       <c r="AB21" t="inlineStr">
         <is>
-          <t>14:58</t>
+          <t>14:26</t>
         </is>
       </c>
       <c r="AD21" t="b">
@@ -2951,10 +2951,10 @@
     </row>
     <row r="22">
       <c r="A22" t="n">
-        <v>120339771</v>
+        <v>120339080</v>
       </c>
       <c r="B22" t="n">
-        <v>79623</v>
+        <v>95225</v>
       </c>
       <c r="C22" t="inlineStr">
         <is>
@@ -2963,38 +2963,38 @@
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E22" t="n">
-        <v>6458</v>
+        <v>2869</v>
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Bollvitmossa</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sphagnum wulfianum</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>Girg.</t>
         </is>
       </c>
       <c r="I22" t="inlineStr"/>
       <c r="P22" t="inlineStr">
         <is>
-          <t>Långtjärnshöjden, Långtjärnshöjden, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q22" t="n">
-        <v>580423</v>
+        <v>580337</v>
       </c>
       <c r="R22" t="n">
-        <v>7056076</v>
+        <v>7056214</v>
       </c>
       <c r="S22" t="n">
         <v>10</v>
@@ -3026,7 +3026,7 @@
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
@@ -3036,7 +3036,7 @@
       </c>
       <c r="AB22" t="inlineStr">
         <is>
-          <t>14:31</t>
+          <t>13:53</t>
         </is>
       </c>
       <c r="AD22" t="b">
@@ -3063,10 +3063,10 @@
     </row>
     <row r="23">
       <c r="A23" t="n">
-        <v>120340499</v>
+        <v>120339582</v>
       </c>
       <c r="B23" t="n">
-        <v>78542</v>
+        <v>90923</v>
       </c>
       <c r="C23" t="inlineStr">
         <is>
@@ -3075,25 +3075,25 @@
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E23" t="n">
-        <v>6425</v>
+        <v>2062</v>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ulltickeporing</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Skeletocutis brevispora</t>
         </is>
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>Niemelä</t>
         </is>
       </c>
       <c r="I23" t="inlineStr"/>
@@ -3103,10 +3103,10 @@
         </is>
       </c>
       <c r="Q23" t="n">
-        <v>580356</v>
+        <v>580409</v>
       </c>
       <c r="R23" t="n">
-        <v>7056158</v>
+        <v>7056174</v>
       </c>
       <c r="S23" t="n">
         <v>10</v>
@@ -3138,7 +3138,7 @@
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
@@ -3148,7 +3148,7 @@
       </c>
       <c r="AB23" t="inlineStr">
         <is>
-          <t>15:02</t>
+          <t>14:33</t>
         </is>
       </c>
       <c r="AD23" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -1467,10 +1467,10 @@
     </row>
     <row r="9">
       <c r="A9" t="n">
-        <v>120339495</v>
+        <v>120339013</v>
       </c>
       <c r="B9" t="n">
-        <v>90864</v>
+        <v>57473</v>
       </c>
       <c r="C9" t="inlineStr">
         <is>
@@ -1483,37 +1483,51 @@
         </is>
       </c>
       <c r="E9" t="n">
-        <v>658</v>
+        <v>103021</v>
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>i par</t>
+        </is>
+      </c>
+      <c r="M9" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P9" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q9" t="n">
-        <v>580409</v>
+        <v>580332</v>
       </c>
       <c r="R9" t="n">
-        <v>7056155</v>
+        <v>7056217</v>
       </c>
       <c r="S9" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T9" t="inlineStr">
         <is>
@@ -1542,7 +1556,7 @@
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -1552,7 +1566,7 @@
       </c>
       <c r="AB9" t="inlineStr">
         <is>
-          <t>14:28</t>
+          <t>13:50</t>
         </is>
       </c>
       <c r="AD9" t="b">
@@ -1567,22 +1581,22 @@
       <c r="AT9" t="inlineStr"/>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>Kim Hultgren</t>
+          <t>Kamilla Andersson</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="n">
-        <v>120339013</v>
+        <v>120339495</v>
       </c>
       <c r="B10" t="n">
-        <v>57473</v>
+        <v>90864</v>
       </c>
       <c r="C10" t="inlineStr">
         <is>
@@ -1595,51 +1609,37 @@
         </is>
       </c>
       <c r="E10" t="n">
-        <v>103021</v>
+        <v>658</v>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>i par</t>
-        </is>
-      </c>
-      <c r="M10" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr"/>
       <c r="P10" t="inlineStr">
         <is>
-          <t>Långtjärnflon, Långtjärnflon, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q10" t="n">
-        <v>580332</v>
+        <v>580409</v>
       </c>
       <c r="R10" t="n">
-        <v>7056217</v>
+        <v>7056155</v>
       </c>
       <c r="S10" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T10" t="inlineStr">
         <is>
@@ -1668,7 +1668,7 @@
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -1678,7 +1678,7 @@
       </c>
       <c r="AB10" t="inlineStr">
         <is>
-          <t>13:50</t>
+          <t>14:28</t>
         </is>
       </c>
       <c r="AD10" t="b">
@@ -1693,12 +1693,12 @@
       <c r="AT10" t="inlineStr"/>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>Kamilla Andersson</t>
+          <t>Kim Hultgren</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
@@ -2377,10 +2377,10 @@
     </row>
     <row r="17">
       <c r="A17" t="n">
-        <v>120339052</v>
+        <v>120339934</v>
       </c>
       <c r="B17" t="n">
-        <v>78542</v>
+        <v>97930</v>
       </c>
       <c r="C17" t="inlineStr">
         <is>
@@ -2389,38 +2389,42 @@
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E17" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Okänd, Okänd, Ång</t>
+          <t>Sollefteå, Sollefteå, Ång</t>
         </is>
       </c>
       <c r="Q17" t="n">
-        <v>580329</v>
+        <v>580411</v>
       </c>
       <c r="R17" t="n">
-        <v>7056169</v>
+        <v>7056094</v>
       </c>
       <c r="S17" t="n">
         <v>10</v>
@@ -2452,7 +2456,7 @@
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
@@ -2462,7 +2466,7 @@
       </c>
       <c r="AB17" t="inlineStr">
         <is>
-          <t>14:02</t>
+          <t>14:46</t>
         </is>
       </c>
       <c r="AD17" t="b">
@@ -2489,10 +2493,10 @@
     </row>
     <row r="18">
       <c r="A18" t="n">
-        <v>120339934</v>
+        <v>120339052</v>
       </c>
       <c r="B18" t="n">
-        <v>97930</v>
+        <v>78542</v>
       </c>
       <c r="C18" t="inlineStr">
         <is>
@@ -2501,42 +2505,38 @@
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E18" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr"/>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Sollefteå, Sollefteå, Ång</t>
+          <t>Okänd, Okänd, Ång</t>
         </is>
       </c>
       <c r="Q18" t="n">
-        <v>580411</v>
+        <v>580329</v>
       </c>
       <c r="R18" t="n">
-        <v>7056094</v>
+        <v>7056169</v>
       </c>
       <c r="S18" t="n">
         <v>10</v>
@@ -2568,7 +2568,7 @@
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
@@ -2578,7 +2578,7 @@
       </c>
       <c r="AB18" t="inlineStr">
         <is>
-          <t>14:46</t>
+          <t>14:02</t>
         </is>
       </c>
       <c r="AD18" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369869</v>
+        <v>124369805</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,43 +3302,34 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580344</v>
+        <v>580354</v>
       </c>
       <c r="R25" t="n">
-        <v>7056210</v>
+        <v>7056221</v>
       </c>
       <c r="S25" t="n">
         <v>30</v>
@@ -3370,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124371145</v>
+        <v>124369869</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,37 +3414,46 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M26" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580411</v>
+        <v>580344</v>
       </c>
       <c r="R26" t="n">
-        <v>7056182</v>
+        <v>7056210</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3482,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370309</v>
+        <v>124370814</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,42 +3531,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580358</v>
+        <v>580405</v>
       </c>
       <c r="R27" t="n">
-        <v>7056205</v>
+        <v>7056179</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3598,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3608,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3635,7 +3631,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369805</v>
+        <v>124370931</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3675,13 +3671,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580354</v>
+        <v>580411</v>
       </c>
       <c r="R28" t="n">
-        <v>7056221</v>
+        <v>7056189</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3710,7 +3706,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3716,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3871,38 +3867,42 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R30" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370814</v>
+        <v>124371145</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R31" t="n">
-        <v>7056179</v>
+        <v>7056182</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369805</v>
+        <v>124370814</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3326,13 +3326,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580354</v>
+        <v>580405</v>
       </c>
       <c r="R25" t="n">
-        <v>7056221</v>
+        <v>7056179</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370814</v>
+        <v>124370931</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3535,21 +3535,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3559,10 +3559,10 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R27" t="n">
-        <v>7056179</v>
+        <v>7056189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,7 +3631,7 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370931</v>
+        <v>124369805</v>
       </c>
       <c r="B28" t="n">
         <v>78810</v>
@@ -3671,13 +3671,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580411</v>
+        <v>580354</v>
       </c>
       <c r="R28" t="n">
-        <v>7056189</v>
+        <v>7056221</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,7 +3706,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3716,7 +3716,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,10 +3743,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370946</v>
+        <v>124370309</v>
       </c>
       <c r="B29" t="n">
-        <v>91012</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,38 +3755,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>1202</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580408</v>
+        <v>580358</v>
       </c>
       <c r="R29" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3818,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3828,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370309</v>
+        <v>124370946</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,42 +3871,38 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580358</v>
+        <v>580408</v>
       </c>
       <c r="R30" t="n">
-        <v>7056205</v>
+        <v>7056189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370814</v>
+        <v>124370931</v>
       </c>
       <c r="B25" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,21 +3302,21 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I25" t="inlineStr"/>
@@ -3326,10 +3326,10 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R25" t="n">
-        <v>7056179</v>
+        <v>7056189</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369869</v>
+        <v>124370946</v>
       </c>
       <c r="B26" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,46 +3414,37 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M26" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580344</v>
+        <v>580408</v>
       </c>
       <c r="R26" t="n">
-        <v>7056210</v>
+        <v>7056189</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3482,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,38 +3522,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R27" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3743,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370309</v>
+        <v>124369869</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,30 +3750,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580358</v>
+        <v>580344</v>
       </c>
       <c r="R29" t="n">
-        <v>7056205</v>
+        <v>7056210</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370946</v>
+        <v>124370814</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580408</v>
+        <v>580405</v>
       </c>
       <c r="R30" t="n">
-        <v>7056189</v>
+        <v>7056179</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD30" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,38 +3298,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R25" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,10 +3402,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370946</v>
+        <v>124371145</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,21 +3418,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3438,10 +3442,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580408</v>
+        <v>580411</v>
       </c>
       <c r="R26" t="n">
-        <v>7056189</v>
+        <v>7056182</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370309</v>
+        <v>124370946</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,42 +3526,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580358</v>
+        <v>580408</v>
       </c>
       <c r="R27" t="n">
-        <v>7056205</v>
+        <v>7056189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369805</v>
+        <v>124370814</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,13 +3666,13 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580354</v>
+        <v>580405</v>
       </c>
       <c r="R28" t="n">
-        <v>7056221</v>
+        <v>7056179</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369869</v>
+        <v>124369805</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,43 +3754,34 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580344</v>
+        <v>580354</v>
       </c>
       <c r="R29" t="n">
-        <v>7056210</v>
+        <v>7056221</v>
       </c>
       <c r="S29" t="n">
         <v>30</v>
@@ -3822,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370814</v>
+        <v>124369869</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,37 +3866,46 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580405</v>
+        <v>580344</v>
       </c>
       <c r="R30" t="n">
-        <v>7056179</v>
+        <v>7056210</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,7 +3971,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124371145</v>
+        <v>124370931</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4014,7 +4014,7 @@
         <v>580411</v>
       </c>
       <c r="R31" t="n">
-        <v>7056182</v>
+        <v>7056189</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370309</v>
+        <v>124369869</v>
       </c>
       <c r="B25" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,30 +3298,35 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
@@ -3330,13 +3335,13 @@
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580358</v>
+        <v>580344</v>
       </c>
       <c r="R25" t="n">
-        <v>7056205</v>
+        <v>7056210</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3365,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3375,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3402,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124371145</v>
+        <v>124370946</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3418,21 +3423,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3442,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580411</v>
+        <v>580408</v>
       </c>
       <c r="R26" t="n">
-        <v>7056182</v>
+        <v>7056189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370946</v>
+        <v>124370931</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,21 +3535,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3554,7 +3559,7 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580408</v>
+        <v>580411</v>
       </c>
       <c r="R27" t="n">
         <v>7056189</v>
@@ -3850,10 +3855,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369869</v>
+        <v>124370309</v>
       </c>
       <c r="B30" t="n">
-        <v>56714</v>
+        <v>98101</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3862,35 +3867,30 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>102612</v>
+        <v>220787</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr">
         <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M30" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
+          <t>150</t>
         </is>
       </c>
       <c r="P30" t="inlineStr">
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580344</v>
+        <v>580358</v>
       </c>
       <c r="R30" t="n">
-        <v>7056210</v>
+        <v>7056205</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,7 +3971,7 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370931</v>
+        <v>124371145</v>
       </c>
       <c r="B31" t="n">
         <v>78810</v>
@@ -4014,7 +4014,7 @@
         <v>580411</v>
       </c>
       <c r="R31" t="n">
-        <v>7056189</v>
+        <v>7056182</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369869</v>
+        <v>124370946</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,46 +3302,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580344</v>
+        <v>580408</v>
       </c>
       <c r="R25" t="n">
-        <v>7056210</v>
+        <v>7056189</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3370,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370946</v>
+        <v>124371145</v>
       </c>
       <c r="B26" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3423,21 +3414,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3447,10 +3438,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580408</v>
+        <v>580411</v>
       </c>
       <c r="R26" t="n">
-        <v>7056189</v>
+        <v>7056182</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3482,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3519,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,38 +3522,42 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R27" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3594,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370814</v>
+        <v>124369869</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>56714</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3647,37 +3642,46 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>102612</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580405</v>
+        <v>580344</v>
       </c>
       <c r="R28" t="n">
-        <v>7056179</v>
+        <v>7056210</v>
       </c>
       <c r="S28" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,7 +3710,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3716,7 +3720,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,7 +3747,7 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369805</v>
+        <v>124370931</v>
       </c>
       <c r="B29" t="n">
         <v>78810</v>
@@ -3783,13 +3787,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580354</v>
+        <v>580411</v>
       </c>
       <c r="R29" t="n">
-        <v>7056221</v>
+        <v>7056189</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3818,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3828,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3855,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370309</v>
+        <v>124369805</v>
       </c>
       <c r="B30" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3867,45 +3871,41 @@
       </c>
       <c r="D30" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E30" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I30" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr"/>
       <c r="P30" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580358</v>
+        <v>580354</v>
       </c>
       <c r="R30" t="n">
-        <v>7056205</v>
+        <v>7056221</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124371145</v>
+        <v>124370814</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580411</v>
+        <v>580405</v>
       </c>
       <c r="R31" t="n">
-        <v>7056182</v>
+        <v>7056179</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370946</v>
+        <v>124369869</v>
       </c>
       <c r="B25" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,37 +3302,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580408</v>
+        <v>580344</v>
       </c>
       <c r="R25" t="n">
-        <v>7056189</v>
+        <v>7056210</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3510,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370309</v>
+        <v>124370946</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91012</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,42 +3531,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>1202</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580358</v>
+        <v>580408</v>
       </c>
       <c r="R27" t="n">
-        <v>7056205</v>
+        <v>7056189</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369869</v>
+        <v>124369805</v>
       </c>
       <c r="B28" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,43 +3647,34 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M28" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580344</v>
+        <v>580354</v>
       </c>
       <c r="R28" t="n">
-        <v>7056210</v>
+        <v>7056221</v>
       </c>
       <c r="S28" t="n">
         <v>30</v>
@@ -3710,7 +3706,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3720,7 +3716,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3747,10 +3743,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B29" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3759,38 +3755,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R29" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369805</v>
+        <v>124370814</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580354</v>
+        <v>580405</v>
       </c>
       <c r="R30" t="n">
-        <v>7056221</v>
+        <v>7056179</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370814</v>
+        <v>124370931</v>
       </c>
       <c r="B31" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,10 +4011,10 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R31" t="n">
-        <v>7056179</v>
+        <v>7056189</v>
       </c>
       <c r="S31" t="n">
         <v>10</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369869</v>
+        <v>124371145</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,46 +3302,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580344</v>
+        <v>580411</v>
       </c>
       <c r="R25" t="n">
-        <v>7056210</v>
+        <v>7056182</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3370,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3407,7 +3398,7 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124371145</v>
+        <v>124369805</v>
       </c>
       <c r="B26" t="n">
         <v>78810</v>
@@ -3447,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580411</v>
+        <v>580354</v>
       </c>
       <c r="R26" t="n">
-        <v>7056182</v>
+        <v>7056221</v>
       </c>
       <c r="S26" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3482,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3492,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3631,10 +3622,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124369805</v>
+        <v>124370309</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3643,41 +3634,45 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580354</v>
+        <v>580358</v>
       </c>
       <c r="R28" t="n">
-        <v>7056221</v>
+        <v>7056205</v>
       </c>
       <c r="S28" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T28" t="inlineStr">
         <is>
@@ -3706,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3716,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370309</v>
+        <v>124370814</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,42 +3750,38 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580358</v>
+        <v>580405</v>
       </c>
       <c r="R29" t="n">
-        <v>7056205</v>
+        <v>7056179</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3822,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3850,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370814</v>
+        <v>124370931</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3866,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3890,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R30" t="n">
-        <v>7056179</v>
+        <v>7056189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370931</v>
+        <v>124369869</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,37 +3978,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580411</v>
+        <v>580344</v>
       </c>
       <c r="R31" t="n">
-        <v>7056189</v>
+        <v>7056210</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3398,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124369805</v>
+        <v>124370814</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,21 +3414,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3438,13 +3438,13 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580354</v>
+        <v>580405</v>
       </c>
       <c r="R26" t="n">
-        <v>7056221</v>
+        <v>7056179</v>
       </c>
       <c r="S26" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T26" t="inlineStr">
         <is>
@@ -3473,7 +3473,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3483,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370946</v>
+        <v>124369869</v>
       </c>
       <c r="B27" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,37 +3526,46 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580408</v>
+        <v>580344</v>
       </c>
       <c r="R27" t="n">
-        <v>7056189</v>
+        <v>7056210</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3585,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3595,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3622,10 +3631,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370309</v>
+        <v>124370931</v>
       </c>
       <c r="B28" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3634,42 +3643,38 @@
       </c>
       <c r="D28" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E28" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I28" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr"/>
       <c r="P28" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580358</v>
+        <v>580411</v>
       </c>
       <c r="R28" t="n">
-        <v>7056205</v>
+        <v>7056189</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,7 +3706,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3716,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,10 +3743,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370814</v>
+        <v>124370309</v>
       </c>
       <c r="B29" t="n">
-        <v>91299</v>
+        <v>98101</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3750,38 +3755,42 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>658</v>
+        <v>220787</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580405</v>
+        <v>580358</v>
       </c>
       <c r="R29" t="n">
-        <v>7056179</v>
+        <v>7056205</v>
       </c>
       <c r="S29" t="n">
         <v>10</v>
@@ -3813,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3823,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3850,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370931</v>
+        <v>124370946</v>
       </c>
       <c r="B30" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3866,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3890,7 +3899,7 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580411</v>
+        <v>580408</v>
       </c>
       <c r="R30" t="n">
         <v>7056189</v>
@@ -3962,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369869</v>
+        <v>124369805</v>
       </c>
       <c r="B31" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3978,43 +3987,34 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M31" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr"/>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580344</v>
+        <v>580354</v>
       </c>
       <c r="R31" t="n">
-        <v>7056210</v>
+        <v>7056221</v>
       </c>
       <c r="S31" t="n">
         <v>30</v>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124371145</v>
+        <v>124369869</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>56714</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,37 +3302,46 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>102612</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M25" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580411</v>
+        <v>580344</v>
       </c>
       <c r="R25" t="n">
-        <v>7056182</v>
+        <v>7056210</v>
       </c>
       <c r="S25" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3361,7 +3370,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3380,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,10 +3407,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370814</v>
+        <v>124371145</v>
       </c>
       <c r="B26" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3414,21 +3423,21 @@
         </is>
       </c>
       <c r="E26" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I26" t="inlineStr"/>
@@ -3438,10 +3447,10 @@
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R26" t="n">
-        <v>7056179</v>
+        <v>7056182</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3482,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3492,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3519,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369869</v>
+        <v>124369805</v>
       </c>
       <c r="B27" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3526,43 +3535,34 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M27" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580344</v>
+        <v>580354</v>
       </c>
       <c r="R27" t="n">
-        <v>7056210</v>
+        <v>7056221</v>
       </c>
       <c r="S27" t="n">
         <v>30</v>
@@ -3594,7 +3594,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3604,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370946</v>
+        <v>124370814</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>91299</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>658</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580408</v>
+        <v>580405</v>
       </c>
       <c r="R30" t="n">
-        <v>7056189</v>
+        <v>7056179</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369805</v>
+        <v>124370946</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,13 +4011,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580354</v>
+        <v>580408</v>
       </c>
       <c r="R31" t="n">
-        <v>7056221</v>
+        <v>7056189</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124369869</v>
+        <v>124370931</v>
       </c>
       <c r="B25" t="n">
-        <v>56714</v>
+        <v>78810</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3302,46 +3302,37 @@
         </is>
       </c>
       <c r="E25" t="n">
-        <v>102612</v>
+        <v>6425</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M25" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr"/>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580344</v>
+        <v>580411</v>
       </c>
       <c r="R25" t="n">
-        <v>7056210</v>
+        <v>7056189</v>
       </c>
       <c r="S25" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T25" t="inlineStr">
         <is>
@@ -3370,7 +3361,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3380,7 +3371,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3519,10 +3510,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124369805</v>
+        <v>124370309</v>
       </c>
       <c r="B27" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3531,41 +3522,45 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580354</v>
+        <v>580358</v>
       </c>
       <c r="R27" t="n">
-        <v>7056221</v>
+        <v>7056205</v>
       </c>
       <c r="S27" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3594,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3604,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3631,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370931</v>
+        <v>124370814</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3647,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3671,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580411</v>
+        <v>580405</v>
       </c>
       <c r="R28" t="n">
-        <v>7056189</v>
+        <v>7056179</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3706,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3716,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3743,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124370309</v>
+        <v>124369869</v>
       </c>
       <c r="B29" t="n">
-        <v>98101</v>
+        <v>56714</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3755,30 +3750,35 @@
       </c>
       <c r="D29" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E29" t="n">
-        <v>220787</v>
+        <v>102612</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I29" t="inlineStr">
         <is>
-          <t>150</t>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="P29" t="inlineStr">
@@ -3787,13 +3787,13 @@
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580358</v>
+        <v>580344</v>
       </c>
       <c r="R29" t="n">
-        <v>7056205</v>
+        <v>7056210</v>
       </c>
       <c r="S29" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,7 +3822,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3832,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370814</v>
+        <v>124370946</v>
       </c>
       <c r="B30" t="n">
-        <v>91299</v>
+        <v>91012</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>658</v>
+        <v>1202</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,10 +3899,10 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580405</v>
+        <v>580408</v>
       </c>
       <c r="R30" t="n">
-        <v>7056179</v>
+        <v>7056189</v>
       </c>
       <c r="S30" t="n">
         <v>10</v>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370946</v>
+        <v>124369805</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,13 +4011,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580408</v>
+        <v>580354</v>
       </c>
       <c r="R31" t="n">
-        <v>7056189</v>
+        <v>7056221</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3398,10 +3398,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124371145</v>
+        <v>124370309</v>
       </c>
       <c r="B26" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,38 +3410,42 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R26" t="n">
-        <v>7056182</v>
+        <v>7056205</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3473,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3483,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3510,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370309</v>
+        <v>124370814</v>
       </c>
       <c r="B27" t="n">
-        <v>98101</v>
+        <v>91299</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3522,42 +3526,38 @@
       </c>
       <c r="D27" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E27" t="n">
-        <v>220787</v>
+        <v>658</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I27" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr"/>
       <c r="P27" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580358</v>
+        <v>580405</v>
       </c>
       <c r="R27" t="n">
-        <v>7056205</v>
+        <v>7056179</v>
       </c>
       <c r="S27" t="n">
         <v>10</v>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124370814</v>
+        <v>124371145</v>
       </c>
       <c r="B28" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580405</v>
+        <v>580411</v>
       </c>
       <c r="R28" t="n">
-        <v>7056179</v>
+        <v>7056182</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3859,10 +3859,10 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124370946</v>
+        <v>124369805</v>
       </c>
       <c r="B30" t="n">
-        <v>91012</v>
+        <v>78810</v>
       </c>
       <c r="C30" t="inlineStr">
         <is>
@@ -3875,21 +3875,21 @@
         </is>
       </c>
       <c r="E30" t="n">
-        <v>1202</v>
+        <v>6425</v>
       </c>
       <c r="F30" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G30" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H30" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I30" t="inlineStr"/>
@@ -3899,13 +3899,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580408</v>
+        <v>580354</v>
       </c>
       <c r="R30" t="n">
-        <v>7056189</v>
+        <v>7056221</v>
       </c>
       <c r="S30" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3934,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3944,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3971,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124369805</v>
+        <v>124370946</v>
       </c>
       <c r="B31" t="n">
-        <v>78810</v>
+        <v>91012</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,21 +3987,21 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>6425</v>
+        <v>1202</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I31" t="inlineStr"/>
@@ -4011,13 +4011,13 @@
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580354</v>
+        <v>580408</v>
       </c>
       <c r="R31" t="n">
-        <v>7056221</v>
+        <v>7056189</v>
       </c>
       <c r="S31" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD31" t="b">

--- a/artfynd/A 44369-2024 artfynd.xlsx
+++ b/artfynd/A 44369-2024 artfynd.xlsx
@@ -3286,10 +3286,10 @@
     </row>
     <row r="25">
       <c r="A25" t="n">
-        <v>124370931</v>
+        <v>124370309</v>
       </c>
       <c r="B25" t="n">
-        <v>78810</v>
+        <v>98101</v>
       </c>
       <c r="C25" t="inlineStr">
         <is>
@@ -3298,38 +3298,42 @@
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E25" t="n">
-        <v>6425</v>
+        <v>220787</v>
       </c>
       <c r="F25" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I25" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I25" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
       <c r="P25" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q25" t="n">
-        <v>580411</v>
+        <v>580358</v>
       </c>
       <c r="R25" t="n">
-        <v>7056189</v>
+        <v>7056205</v>
       </c>
       <c r="S25" t="n">
         <v>10</v>
@@ -3361,7 +3365,7 @@
       </c>
       <c r="Z25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AA25" t="inlineStr">
@@ -3371,7 +3375,7 @@
       </c>
       <c r="AB25" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:15</t>
         </is>
       </c>
       <c r="AD25" t="b">
@@ -3398,10 +3402,10 @@
     </row>
     <row r="26">
       <c r="A26" t="n">
-        <v>124370309</v>
+        <v>124370931</v>
       </c>
       <c r="B26" t="n">
-        <v>98101</v>
+        <v>78810</v>
       </c>
       <c r="C26" t="inlineStr">
         <is>
@@ -3410,42 +3414,38 @@
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E26" t="n">
-        <v>220787</v>
+        <v>6425</v>
       </c>
       <c r="F26" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I26" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
+          <t>(Ach.) Ach.</t>
+        </is>
+      </c>
+      <c r="I26" t="inlineStr"/>
       <c r="P26" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q26" t="n">
-        <v>580358</v>
+        <v>580411</v>
       </c>
       <c r="R26" t="n">
-        <v>7056205</v>
+        <v>7056189</v>
       </c>
       <c r="S26" t="n">
         <v>10</v>
@@ -3477,7 +3477,7 @@
       </c>
       <c r="Z26" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA26" t="inlineStr">
@@ -3487,7 +3487,7 @@
       </c>
       <c r="AB26" t="inlineStr">
         <is>
-          <t>18:15</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD26" t="b">
@@ -3514,10 +3514,10 @@
     </row>
     <row r="27">
       <c r="A27" t="n">
-        <v>124370814</v>
+        <v>124369805</v>
       </c>
       <c r="B27" t="n">
-        <v>91299</v>
+        <v>78810</v>
       </c>
       <c r="C27" t="inlineStr">
         <is>
@@ -3530,21 +3530,21 @@
         </is>
       </c>
       <c r="E27" t="n">
-        <v>658</v>
+        <v>6425</v>
       </c>
       <c r="F27" t="inlineStr">
         <is>
-          <t>Rosenticka</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G27" t="inlineStr">
         <is>
-          <t>Rhodofomes roseus</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H27" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I27" t="inlineStr"/>
@@ -3554,13 +3554,13 @@
         </is>
       </c>
       <c r="Q27" t="n">
-        <v>580405</v>
+        <v>580354</v>
       </c>
       <c r="R27" t="n">
-        <v>7056179</v>
+        <v>7056221</v>
       </c>
       <c r="S27" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T27" t="inlineStr">
         <is>
@@ -3589,7 +3589,7 @@
       </c>
       <c r="Z27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AA27" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="AB27" t="inlineStr">
         <is>
-          <t>18:28</t>
+          <t>18:04</t>
         </is>
       </c>
       <c r="AD27" t="b">
@@ -3626,10 +3626,10 @@
     </row>
     <row r="28">
       <c r="A28" t="n">
-        <v>124371145</v>
+        <v>124370814</v>
       </c>
       <c r="B28" t="n">
-        <v>78810</v>
+        <v>91299</v>
       </c>
       <c r="C28" t="inlineStr">
         <is>
@@ -3642,21 +3642,21 @@
         </is>
       </c>
       <c r="E28" t="n">
-        <v>6425</v>
+        <v>658</v>
       </c>
       <c r="F28" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Rosenticka</t>
         </is>
       </c>
       <c r="G28" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Rhodofomes roseus</t>
         </is>
       </c>
       <c r="H28" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Alb. &amp; Schwein.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I28" t="inlineStr"/>
@@ -3666,10 +3666,10 @@
         </is>
       </c>
       <c r="Q28" t="n">
-        <v>580411</v>
+        <v>580405</v>
       </c>
       <c r="R28" t="n">
-        <v>7056182</v>
+        <v>7056179</v>
       </c>
       <c r="S28" t="n">
         <v>10</v>
@@ -3701,7 +3701,7 @@
       </c>
       <c r="Z28" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AA28" t="inlineStr">
@@ -3711,7 +3711,7 @@
       </c>
       <c r="AB28" t="inlineStr">
         <is>
-          <t>18:34</t>
+          <t>18:28</t>
         </is>
       </c>
       <c r="AD28" t="b">
@@ -3738,10 +3738,10 @@
     </row>
     <row r="29">
       <c r="A29" t="n">
-        <v>124369869</v>
+        <v>124370946</v>
       </c>
       <c r="B29" t="n">
-        <v>56714</v>
+        <v>91012</v>
       </c>
       <c r="C29" t="inlineStr">
         <is>
@@ -3754,46 +3754,37 @@
         </is>
       </c>
       <c r="E29" t="n">
-        <v>102612</v>
+        <v>1202</v>
       </c>
       <c r="F29" t="inlineStr">
         <is>
-          <t>Järpe</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G29" t="inlineStr">
         <is>
-          <t>Tetrastes bonasia</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H29" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I29" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="M29" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr"/>
       <c r="P29" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q29" t="n">
-        <v>580344</v>
+        <v>580408</v>
       </c>
       <c r="R29" t="n">
-        <v>7056210</v>
+        <v>7056189</v>
       </c>
       <c r="S29" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T29" t="inlineStr">
         <is>
@@ -3822,7 +3813,7 @@
       </c>
       <c r="Z29" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AA29" t="inlineStr">
@@ -3832,7 +3823,7 @@
       </c>
       <c r="AB29" t="inlineStr">
         <is>
-          <t>18:06</t>
+          <t>18:30</t>
         </is>
       </c>
       <c r="AD29" t="b">
@@ -3859,7 +3850,7 @@
     </row>
     <row r="30">
       <c r="A30" t="n">
-        <v>124369805</v>
+        <v>124371145</v>
       </c>
       <c r="B30" t="n">
         <v>78810</v>
@@ -3899,13 +3890,13 @@
         </is>
       </c>
       <c r="Q30" t="n">
-        <v>580354</v>
+        <v>580411</v>
       </c>
       <c r="R30" t="n">
-        <v>7056221</v>
+        <v>7056182</v>
       </c>
       <c r="S30" t="n">
-        <v>30</v>
+        <v>10</v>
       </c>
       <c r="T30" t="inlineStr">
         <is>
@@ -3934,7 +3925,7 @@
       </c>
       <c r="Z30" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AA30" t="inlineStr">
@@ -3944,7 +3935,7 @@
       </c>
       <c r="AB30" t="inlineStr">
         <is>
-          <t>18:04</t>
+          <t>18:34</t>
         </is>
       </c>
       <c r="AD30" t="b">
@@ -3971,10 +3962,10 @@
     </row>
     <row r="31">
       <c r="A31" t="n">
-        <v>124370946</v>
+        <v>124369869</v>
       </c>
       <c r="B31" t="n">
-        <v>91012</v>
+        <v>56714</v>
       </c>
       <c r="C31" t="inlineStr">
         <is>
@@ -3987,37 +3978,46 @@
         </is>
       </c>
       <c r="E31" t="n">
-        <v>1202</v>
+        <v>102612</v>
       </c>
       <c r="F31" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Järpe</t>
         </is>
       </c>
       <c r="G31" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Tetrastes bonasia</t>
         </is>
       </c>
       <c r="H31" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
-        </is>
-      </c>
-      <c r="I31" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="P31" t="inlineStr">
         <is>
           <t>Långtjärnflon, Långtjärnflon, Ång</t>
         </is>
       </c>
       <c r="Q31" t="n">
-        <v>580408</v>
+        <v>580344</v>
       </c>
       <c r="R31" t="n">
-        <v>7056189</v>
+        <v>7056210</v>
       </c>
       <c r="S31" t="n">
-        <v>10</v>
+        <v>30</v>
       </c>
       <c r="T31" t="inlineStr">
         <is>
@@ -4046,7 +4046,7 @@
       </c>
       <c r="Z31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AA31" t="inlineStr">
@@ -4056,7 +4056,7 @@
       </c>
       <c r="AB31" t="inlineStr">
         <is>
-          <t>18:30</t>
+          <t>18:06</t>
         </is>
       </c>
       <c r="AD31" t="b">
